--- a/通信ETF报告/相关表格(已自动还原).xlsx
+++ b/通信ETF报告/相关表格(已自动还原).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\报告\通信ETF报告\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F97E776-D95F-43E0-A1F4-6AA3C21C6941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00329814-C9B6-43CF-9356-D7EA843BAB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
   <si>
     <t>中信预测高速光模块出货</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -455,6 +455,60 @@
   </si>
   <si>
     <t>券商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>广义光占AI基建系数</t>
+  </si>
+  <si>
+    <t>四大云占全球比例约：</t>
+  </si>
+  <si>
+    <t>投向AI基建份额（亿美元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光模块占比份额（亿美元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>广义光通信占比份额（亿美元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightCounting测算份额（亿美元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>光模块占AI基建系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全球市场份额测算（亿美元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完整市场预测（亿元）</t>
+  </si>
+  <si>
+    <t>银河</t>
+  </si>
+  <si>
+    <t>LightCounting预期增长系数：CAGR尺度为22%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,8 +572,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -528,64 +594,71 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
+      <left style="thin">
         <color indexed="64"/>
-      </right>
-      <top style="medium">
+      </left>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -597,7 +670,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -612,51 +685,54 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -939,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z50"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.375" customWidth="1"/>
@@ -952,7 +1028,7 @@
     <col min="9" max="9" width="8.875" customWidth="1"/>
     <col min="10" max="10" width="8.625" customWidth="1"/>
     <col min="12" max="12" width="15.75" customWidth="1"/>
-    <col min="21" max="21" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
@@ -1224,7 +1300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1253,7 +1329,7 @@
         <v>219.5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1282,7 +1358,7 @@
         <v>119.2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1311,7 +1387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1470,12 +1546,12 @@
         <v>744</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1501,7 +1577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1515,14 +1591,14 @@
       <c r="D19" s="2">
         <v>185</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="30">
         <f>(D19*F19)^0.5</f>
         <v>206.7244542863761</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="10">
         <v>231</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="30">
         <f>(F19*H19)^0.5</f>
         <v>260.603146565808</v>
       </c>
@@ -1530,7 +1606,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1546,36 +1622,39 @@
       <c r="E20" s="2">
         <v>477</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="31">
         <f>E20*(1+$F$25)</f>
         <v>548.54999999999995</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="31">
         <f t="shared" ref="G20:H20" si="2">F20*(1+$F$25)</f>
         <v>630.83249999999987</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="31">
         <f t="shared" si="2"/>
         <v>725.45737499999984</v>
       </c>
-      <c r="U20" s="10"/>
-      <c r="V20" s="11" t="s">
+      <c r="U20" s="12"/>
+      <c r="V20" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="W20" s="11" t="s">
+      <c r="W20" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="X20" s="11" t="s">
+      <c r="X20" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="Y20" s="11" t="s">
+      <c r="Y20" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="Z20" s="11" t="s">
+      <c r="Z20" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA20" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1591,19 +1670,19 @@
       <c r="E21" s="2">
         <v>242</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="31">
         <f t="shared" ref="F21:H24" si="3">E21*(1+$F$25)</f>
         <v>278.29999999999995</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="31">
         <f t="shared" si="3"/>
         <v>320.0449999999999</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="31">
         <f t="shared" si="3"/>
         <v>368.05174999999986</v>
       </c>
-      <c r="U21" s="12" t="s">
+      <c r="U21" s="13" t="s">
         <v>63</v>
       </c>
       <c r="V21" s="13">
@@ -1619,11 +1698,14 @@
         <v>1350</v>
       </c>
       <c r="Z21" s="13">
-        <f>SUM(V21:Y21)</f>
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+        <v>1300</v>
+      </c>
+      <c r="AA21" s="13">
+        <f>SUM(V21:Z21)</f>
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -1639,19 +1721,19 @@
       <c r="E22" s="2">
         <v>1010</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="31">
         <f t="shared" si="3"/>
         <v>1161.5</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="31">
         <f t="shared" si="3"/>
         <v>1335.7249999999999</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="31">
         <f t="shared" si="3"/>
         <v>1536.0837499999998</v>
       </c>
-      <c r="U22" s="12" t="s">
+      <c r="U22" s="13" t="s">
         <v>64</v>
       </c>
       <c r="V22" s="14">
@@ -1666,42 +1748,44 @@
       <c r="Y22" s="14">
         <v>0.72499999999999998</v>
       </c>
-      <c r="Z22" s="14">
+      <c r="Z22" s="15">
         <v>0.72499999999999998</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA22" s="14">
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="2">
-        <v>225</v>
+      <c r="B23" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="C23" s="2">
-        <f>B23*(1+C25)</f>
-        <v>337.5</v>
-      </c>
-      <c r="D23" s="2">
+        <v>255</v>
+      </c>
+      <c r="D23" s="32">
         <f t="shared" ref="D23:E23" si="4">C23*(1+D25)</f>
-        <v>421.875</v>
-      </c>
-      <c r="E23" s="2">
+        <v>318.75</v>
+      </c>
+      <c r="E23" s="32">
         <f t="shared" si="4"/>
-        <v>527.34375</v>
-      </c>
-      <c r="F23" s="23">
+        <v>398.4375</v>
+      </c>
+      <c r="F23" s="31">
         <f t="shared" si="3"/>
-        <v>606.4453125</v>
-      </c>
-      <c r="G23" s="23">
+        <v>458.20312499999994</v>
+      </c>
+      <c r="G23" s="31">
         <f t="shared" si="3"/>
-        <v>697.412109375</v>
-      </c>
-      <c r="H23" s="23">
+        <v>526.93359374999989</v>
+      </c>
+      <c r="H23" s="31">
         <f t="shared" si="3"/>
-        <v>802.02392578124989</v>
-      </c>
-      <c r="U23" s="12" t="s">
+        <v>605.97363281249977</v>
+      </c>
+      <c r="U23" s="13" t="s">
         <v>65</v>
       </c>
       <c r="V23" s="13">
@@ -1716,43 +1800,47 @@
       <c r="Y23" s="13">
         <v>978.75</v>
       </c>
-      <c r="Z23" s="13">
-        <f>SUM(V23:Y23)</f>
-        <v>5075</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Z23" s="16">
+        <f>Z22*Z21</f>
+        <v>942.5</v>
+      </c>
+      <c r="AA23" s="13">
+        <f>SUM(V23:Z23)</f>
+        <v>6017.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24" s="2">
         <v>217</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="32">
         <f>B24*(1+C25)</f>
         <v>325.5</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="32">
         <f t="shared" ref="D24:E24" si="5">C24*(1+D25)</f>
         <v>406.875</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="32">
         <f t="shared" si="5"/>
         <v>508.59375</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="31">
         <f t="shared" si="3"/>
         <v>584.8828125</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="31">
         <f t="shared" si="3"/>
         <v>672.615234375</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="31">
         <f t="shared" si="3"/>
         <v>773.50751953124995</v>
       </c>
-      <c r="U24" s="12" t="s">
+      <c r="U24" s="13" t="s">
         <v>70</v>
       </c>
       <c r="V24" s="17">
@@ -1770,8 +1858,11 @@
       <c r="Z24" s="17">
         <v>6.5000000000000002E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA24" s="17">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1793,7 +1884,7 @@
       <c r="H25">
         <v>0.11</v>
       </c>
-      <c r="U25" s="12" t="s">
+      <c r="U25" s="13" t="s">
         <v>71</v>
       </c>
       <c r="V25" s="14">
@@ -1811,33 +1902,68 @@
       <c r="Z25" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="U26" s="12" t="s">
+      <c r="AA25" s="14">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <f>1+C25</f>
+        <v>1.5</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:H26" si="6">1+D25</f>
+        <v>1.25</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="6"/>
+        <v>1.25</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="6"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="6"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="6"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="U26" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="V26" s="18">
+      <c r="V26" s="16">
         <f>V24*V23</f>
         <v>94.25</v>
       </c>
-      <c r="W26" s="18">
-        <f t="shared" ref="W26:Y26" si="6">W24*W23</f>
+      <c r="W26" s="16">
+        <f t="shared" ref="W26:Y26" si="7">W24*W23</f>
         <v>94.25</v>
       </c>
-      <c r="X26" s="18">
-        <f t="shared" si="6"/>
+      <c r="X26" s="16">
+        <f t="shared" si="7"/>
         <v>77.756250000000009</v>
       </c>
-      <c r="Y26" s="18">
-        <f t="shared" si="6"/>
+      <c r="Y26" s="16">
+        <f t="shared" si="7"/>
         <v>63.618750000000006</v>
       </c>
-      <c r="Z26" s="13">
-        <f>SUM(V26:Y26)</f>
-        <v>329.875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Z26" s="16">
+        <f>Z24*Z23</f>
+        <v>61.262500000000003</v>
+      </c>
+      <c r="AA26" s="16">
+        <f>SUM(V26:Z26)</f>
+        <v>391.13749999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <f>PRODUCT(C26:H26)^(1/6)</f>
+        <v>1.2286786845872844</v>
+      </c>
       <c r="J27" s="4" t="s">
         <v>16</v>
       </c>
@@ -1853,7 +1979,7 @@
       <c r="N27" t="s">
         <v>15</v>
       </c>
-      <c r="U27" s="15" t="s">
+      <c r="U27" s="18" t="s">
         <v>67</v>
       </c>
       <c r="V27" s="19">
@@ -1861,23 +1987,27 @@
         <v>50.750000000000007</v>
       </c>
       <c r="W27" s="19">
-        <f t="shared" ref="W27:Y27" si="7">W25*W23</f>
+        <f t="shared" ref="W27:Y27" si="8">W25*W23</f>
         <v>50.750000000000007</v>
       </c>
       <c r="X27" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>41.868750000000006</v>
       </c>
       <c r="Y27" s="19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>34.256250000000001</v>
       </c>
-      <c r="Z27" s="13">
-        <f>SUM(V27:Y27)</f>
-        <v>177.62500000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Z27" s="19">
+        <f>Z25*Z23</f>
+        <v>32.987500000000004</v>
+      </c>
+      <c r="AA27" s="16">
+        <f>SUM(V27:Z27)</f>
+        <v>210.61250000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="J28" s="4" t="s">
         <v>17</v>
       </c>
@@ -1894,7 +2024,7 @@
       <c r="N28" s="3">
         <v>0.47</v>
       </c>
-      <c r="U28" s="12" t="s">
+      <c r="U28" s="13" t="s">
         <v>68</v>
       </c>
       <c r="V28" s="14">
@@ -1912,8 +2042,11 @@
       <c r="Z28" s="14">
         <v>3.1E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA28" s="14">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="J29" s="4" t="s">
         <v>18</v>
       </c>
@@ -1933,44 +2066,47 @@
         <f>1-N28</f>
         <v>0.53</v>
       </c>
-      <c r="U29" s="15" t="s">
+      <c r="U29" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="V29" s="16">
+      <c r="V29" s="18">
         <v>62</v>
       </c>
-      <c r="W29" s="16">
+      <c r="W29" s="18">
         <v>62</v>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="18">
         <v>51.15</v>
       </c>
-      <c r="Y29" s="16">
+      <c r="Y29" s="18">
         <v>41.85</v>
       </c>
-      <c r="Z29" s="13">
-        <f>SUM(V29:Y29)</f>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="U30" s="20" t="s">
+      <c r="Z29" s="18">
+        <v>41.85</v>
+      </c>
+      <c r="AA29" s="13">
+        <f>SUM(V29:Z29)</f>
+        <v>258.85000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="U30" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="V30" s="5">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="U31" s="21" t="s">
+      <c r="V30" s="20">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="U31" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="V31">
-        <f>Z27/V30</f>
-        <v>253.75000000000006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="V31" s="21">
+        <f>AA27/V30</f>
+        <v>263.26562500000006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -1993,7 +2129,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -2017,7 +2153,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -2026,19 +2162,19 @@
         <v>0.24999999999999997</v>
       </c>
       <c r="C34" s="3">
-        <f t="shared" ref="C34:F34" si="8">C33/7*5</f>
+        <f t="shared" ref="C34:F34" si="9">C33/7*5</f>
         <v>0.14285714285714288</v>
       </c>
       <c r="D34" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10714285714285715</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.5714285714285715E-2</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="G34" s="5">
@@ -2046,7 +2182,7 @@
         <v>0.6428571428571429</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2056,8 +2192,27 @@
       <c r="C35" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U35" s="21"/>
+      <c r="V35" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="W35" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="X35" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y35" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z35" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA35" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2067,8 +2222,29 @@
       <c r="C36" s="2">
         <v>248.42</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U36" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="V36" s="21">
+        <v>2000</v>
+      </c>
+      <c r="W36" s="21">
+        <v>2000</v>
+      </c>
+      <c r="X36" s="21">
+        <v>1650</v>
+      </c>
+      <c r="Y36" s="21">
+        <v>1350</v>
+      </c>
+      <c r="Z36" s="21">
+        <v>1300</v>
+      </c>
+      <c r="AA36" s="21">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -2078,8 +2254,29 @@
       <c r="C37" s="6">
         <v>0.99719999999999998</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U37" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="V37" s="27">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="W37" s="27">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="X37" s="27">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="Y37" s="27">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="Z37" s="27">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AA37" s="27">
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -2091,20 +2288,129 @@
         <f>C37*C36</f>
         <v>247.72442399999997</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U38" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="V38" s="21">
+        <v>1450</v>
+      </c>
+      <c r="W38" s="21">
+        <v>1450</v>
+      </c>
+      <c r="X38" s="21">
+        <v>1196.25</v>
+      </c>
+      <c r="Y38" s="21">
+        <v>978.75</v>
+      </c>
+      <c r="Z38" s="21">
+        <v>942.5</v>
+      </c>
+      <c r="AA38" s="21">
+        <v>5075</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B39" s="6">
         <f>C33/B33</f>
         <v>0.57142857142857151</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U39" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="V39" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="W39" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="X39" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="Y39" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="Z39" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AA39" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B40" s="8">
         <f>C38/B38</f>
         <v>0.66206560137264159</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U40" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="V40" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="W40" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="X40" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y40" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Z40" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AA40" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="U41" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="V41" s="21">
+        <v>94.25</v>
+      </c>
+      <c r="W41" s="21">
+        <v>94.25</v>
+      </c>
+      <c r="X41" s="21">
+        <v>77.756250000000009</v>
+      </c>
+      <c r="Y41" s="21">
+        <v>63.618750000000006</v>
+      </c>
+      <c r="Z41" s="21">
+        <v>61.262500000000003</v>
+      </c>
+      <c r="AA41" s="21">
+        <v>329.875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="U42" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="V42" s="21">
+        <v>50.750000000000007</v>
+      </c>
+      <c r="W42" s="21">
+        <v>50.750000000000007</v>
+      </c>
+      <c r="X42" s="21">
+        <v>41.868750000000006</v>
+      </c>
+      <c r="Y42" s="21">
+        <v>34.256250000000001</v>
+      </c>
+      <c r="Z42" s="21">
+        <v>32.987500000000004</v>
+      </c>
+      <c r="AA42" s="21">
+        <v>210.61250000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B43" s="5">
         <v>0.25</v>
       </c>
@@ -2112,16 +2418,58 @@
         <f>C44/B45</f>
         <v>0.16548637092463922</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U43" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="V43" s="28">
+        <v>3.1E-2</v>
+      </c>
+      <c r="W43" s="28">
+        <v>3.1E-2</v>
+      </c>
+      <c r="X43" s="28">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Y43" s="28">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Z43" s="28">
+        <v>3.1E-2</v>
+      </c>
+      <c r="AA43" s="28">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>374.2</v>
       </c>
       <c r="C44">
         <v>247.7</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U44" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="V44" s="21">
+        <v>62</v>
+      </c>
+      <c r="W44" s="23">
+        <v>62</v>
+      </c>
+      <c r="X44" s="23">
+        <v>51.15</v>
+      </c>
+      <c r="Y44" s="23">
+        <v>41.85</v>
+      </c>
+      <c r="Z44" s="23">
+        <v>41.85</v>
+      </c>
+      <c r="AA44" s="23">
+        <v>258.85000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>51</v>
       </c>
@@ -2129,17 +2477,35 @@
         <f>B44/B43</f>
         <v>1496.8</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="U45" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="V45" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="W45" s="25"/>
+      <c r="X45" s="24"/>
+      <c r="Y45" s="24"/>
+      <c r="Z45" s="24"/>
+      <c r="AA45" s="24"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>52</v>
       </c>
       <c r="B46">
-        <f>B45/6.9</f>
-        <v>216.92753623188403</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <f>B45/6.85</f>
+        <v>218.5109489051095</v>
+      </c>
+      <c r="U46" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="V46" s="22">
+        <v>263.26562500000006</v>
+      </c>
+      <c r="W46" s="26"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>81</v>
       </c>
@@ -2218,7 +2584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471C4705-0ADB-4AB9-AEBD-0309CEFFECB6}">
-  <dimension ref="A15:U51"/>
+  <dimension ref="A15:U62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2717,11 +3083,11 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="33" t="s">
         <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="C45" s="2">
         <v>148</v>
@@ -2732,13 +3098,13 @@
       <c r="E45" s="2">
         <v>185</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="30">
         <v>206.7244542863761</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="10">
         <v>231</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="30">
         <v>260.603146565808</v>
       </c>
       <c r="I45" s="2">
@@ -2746,7 +3112,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="25"/>
+      <c r="A46" s="33"/>
       <c r="B46" t="s">
         <v>55</v>
       </c>
@@ -2762,74 +3128,74 @@
       <c r="F46" s="2">
         <v>242</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46" s="31">
         <v>278.29999999999995</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="31">
         <v>320.0449999999999</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I46" s="31">
         <v>368.05174999999986</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="33" t="s">
         <v>109</v>
       </c>
       <c r="B47" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="2">
-        <v>225</v>
+      <c r="C47" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="D47" s="2">
-        <v>337.5</v>
-      </c>
-      <c r="E47" s="2">
-        <v>421.875</v>
-      </c>
-      <c r="F47" s="2">
-        <v>527.34375</v>
-      </c>
-      <c r="G47" s="2">
-        <v>606.4453125</v>
-      </c>
-      <c r="H47" s="2">
-        <v>697.412109375</v>
-      </c>
-      <c r="I47" s="2">
-        <v>802.02392578124989</v>
+        <v>255</v>
+      </c>
+      <c r="E47" s="32">
+        <v>318.75</v>
+      </c>
+      <c r="F47" s="32">
+        <v>398.4375</v>
+      </c>
+      <c r="G47" s="31">
+        <v>458.20312499999994</v>
+      </c>
+      <c r="H47" s="31">
+        <v>526.93359374999989</v>
+      </c>
+      <c r="I47" s="31">
+        <v>605.97363281249977</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="25"/>
+      <c r="A48" s="33"/>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48" s="2">
         <v>217</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="32">
         <v>325.5</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="32">
         <v>406.875</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="32">
         <v>508.59375</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="31">
         <v>584.8828125</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="31">
         <v>672.615234375</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="31">
         <v>773.50751953124995</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="25"/>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="33"/>
       <c r="B49" t="s">
         <v>107</v>
       </c>
@@ -2845,18 +3211,18 @@
       <c r="F49" s="2">
         <v>477</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="31">
         <v>548.54999999999995</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="31">
         <v>630.83249999999987</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="31">
         <v>725.45737499999984</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="24" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="11" t="s">
         <v>110</v>
       </c>
       <c r="B50" t="s">
@@ -2874,44 +3240,251 @@
       <c r="F50" s="2">
         <v>1010</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="31">
         <v>1161.5</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="31">
         <v>1335.7249999999999</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="31">
         <v>1536.0837499999998</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51">
+        <v>0.5</v>
+      </c>
+      <c r="E51">
+        <v>0.25</v>
+      </c>
+      <c r="F51">
+        <v>0.25</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="H51">
+        <v>0.15</v>
+      </c>
+      <c r="I51">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D55" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" t="s">
+        <v>91</v>
+      </c>
+      <c r="G55" t="s">
+        <v>92</v>
+      </c>
+      <c r="H55" t="s">
+        <v>93</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J55" t="s">
+        <v>105</v>
+      </c>
+      <c r="K55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D56" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="2">
+        <v>148</v>
+      </c>
+      <c r="F56" s="2">
+        <v>165.46903033498444</v>
+      </c>
+      <c r="G56" s="2">
+        <v>185</v>
+      </c>
+      <c r="H56" s="30">
+        <v>206.7244542863761</v>
+      </c>
+      <c r="I56" s="10">
+        <v>231</v>
+      </c>
+      <c r="J56" s="30">
+        <v>260.603146565808</v>
+      </c>
+      <c r="K56" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" s="2">
+        <v>170</v>
+      </c>
+      <c r="F57" s="2">
+        <v>205</v>
+      </c>
+      <c r="G57" s="2">
+        <v>220</v>
+      </c>
+      <c r="H57" s="2">
+        <v>242</v>
+      </c>
+      <c r="I57" s="31">
+        <v>278.29999999999995</v>
+      </c>
+      <c r="J57" s="31">
+        <v>320.0449999999999</v>
+      </c>
+      <c r="K57" s="31">
+        <v>368.05174999999986</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D58" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="2">
+        <v>255</v>
+      </c>
+      <c r="G58" s="32">
+        <v>318.75</v>
+      </c>
+      <c r="H58" s="32">
+        <v>398.4375</v>
+      </c>
+      <c r="I58" s="31">
+        <v>458.20312499999994</v>
+      </c>
+      <c r="J58" s="31">
+        <v>526.93359374999989</v>
+      </c>
+      <c r="K58" s="31">
+        <v>605.97363281249977</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D59" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="2">
+        <v>217</v>
+      </c>
+      <c r="F59" s="32">
+        <v>325.5</v>
+      </c>
+      <c r="G59" s="32">
+        <v>406.875</v>
+      </c>
+      <c r="H59" s="32">
+        <v>508.59375</v>
+      </c>
+      <c r="I59" s="31">
+        <v>584.8828125</v>
+      </c>
+      <c r="J59" s="31">
+        <v>672.615234375</v>
+      </c>
+      <c r="K59" s="31">
+        <v>773.50751953124995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D60" t="s">
+        <v>107</v>
+      </c>
+      <c r="E60" s="2">
+        <v>241</v>
+      </c>
+      <c r="F60" s="2">
+        <v>302</v>
+      </c>
+      <c r="G60" s="2">
+        <v>368</v>
+      </c>
+      <c r="H60" s="2">
+        <v>477</v>
+      </c>
+      <c r="I60" s="31">
+        <v>548.54999999999995</v>
+      </c>
+      <c r="J60" s="31">
+        <v>630.83249999999987</v>
+      </c>
+      <c r="K60" s="31">
+        <v>725.45737499999984</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D61" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="2">
+        <v>180</v>
+      </c>
+      <c r="F61" s="2">
+        <v>490</v>
+      </c>
+      <c r="G61" s="2">
+        <v>870</v>
+      </c>
+      <c r="H61" s="2">
+        <v>1010</v>
+      </c>
+      <c r="I61" s="31">
+        <v>1161.5</v>
+      </c>
+      <c r="J61" s="31">
+        <v>1335.7249999999999</v>
+      </c>
+      <c r="K61" s="31">
+        <v>1536.0837499999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D62" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22">
+      <c r="F62">
         <v>0.5</v>
       </c>
-      <c r="E51" s="22">
+      <c r="G62">
         <v>0.25</v>
       </c>
-      <c r="F51" s="22">
+      <c r="H62">
         <v>0.25</v>
       </c>
-      <c r="G51" s="22">
+      <c r="I62" s="4">
         <v>0.15</v>
       </c>
-      <c r="H51" s="22">
+      <c r="J62">
         <v>0.15</v>
       </c>
-      <c r="I51" s="22">
+      <c r="K62">
         <v>0.11</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A51:C51"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
